--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.75844</v>
+        <v>17.06037</v>
       </c>
       <c r="D2" t="n">
-        <v>16.58796</v>
+        <v>16.70335</v>
       </c>
       <c r="E2" t="n">
-        <v>17.1456</v>
+        <v>16.72792</v>
       </c>
       <c r="F2" t="n">
-        <v>43.86224</v>
+        <v>43.31155</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05107</v>
+        <v>0.05119</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82578</v>
+        <v>1.84736</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.95351</v>
+        <v>17.19025</v>
       </c>
       <c r="D3" t="n">
-        <v>16.52549</v>
+        <v>16.89063</v>
       </c>
       <c r="E3" t="n">
-        <v>17.047</v>
+        <v>17.07871</v>
       </c>
       <c r="F3" t="n">
-        <v>43.34129</v>
+        <v>42.77601</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05112</v>
+        <v>0.05132</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8181</v>
+        <v>1.83282</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.62991</v>
+        <v>16.67621</v>
       </c>
       <c r="D4" t="n">
-        <v>16.3989</v>
+        <v>16.59762</v>
       </c>
       <c r="E4" t="n">
-        <v>17.19138</v>
+        <v>16.62598</v>
       </c>
       <c r="F4" t="n">
-        <v>42.71335</v>
+        <v>42.60253</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05189</v>
+        <v>0.05081</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81749</v>
+        <v>1.84366</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87365</v>
+        <v>17.19987</v>
       </c>
       <c r="D6" t="n">
-        <v>16.22887</v>
+        <v>15.7478</v>
       </c>
       <c r="E6" t="n">
-        <v>16.49595</v>
+        <v>16.72877</v>
       </c>
       <c r="F6" t="n">
-        <v>22.20944</v>
+        <v>22.09244</v>
       </c>
       <c r="G6" t="n">
-        <v>35.09826</v>
+        <v>34.99934</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.06786</v>
+        <v>16.73253</v>
       </c>
       <c r="D7" t="n">
-        <v>16.03988</v>
+        <v>16.22778</v>
       </c>
       <c r="E7" t="n">
-        <v>16.70734</v>
+        <v>16.72481</v>
       </c>
       <c r="F7" t="n">
-        <v>21.63021</v>
+        <v>21.965</v>
       </c>
       <c r="G7" t="n">
-        <v>34.95532</v>
+        <v>33.94099</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.03447</v>
+        <v>16.6275</v>
       </c>
       <c r="D8" t="n">
-        <v>16.11046</v>
+        <v>16.47104</v>
       </c>
       <c r="E8" t="n">
-        <v>16.37973</v>
+        <v>16.62153</v>
       </c>
       <c r="F8" t="n">
-        <v>22.28506</v>
+        <v>21.96284</v>
       </c>
       <c r="G8" t="n">
-        <v>34.92559</v>
+        <v>34.60001</v>
       </c>
     </row>
   </sheetData>
